--- a/Intake_FireCatLosses_v1.xlsx
+++ b/Intake_FireCatLosses_v1.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -520,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V103"/>
+  <dimension ref="B1:V120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1164,1081 +1165,1381 @@
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>⟦SECTIONS⟧</t>
+          <t>⟦INVENTORY⟧</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Datasets</t>
+          <t>Holds</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>State</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>History</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>01, 02</t>
+          <t>Premium and loss history per section</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Earthquake</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>EPI Projections</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04</t>
+          <t>Estimated premium income, N and N+1</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Windstorm</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Large Losses</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04</t>
+          <t>Individual large claims, per-risk sections</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Cat Losses</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Catastrophe events, cat sections</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Risk Profiles</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Banded exposure — the per-risk rating basis</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>EQ Aggs</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Earthquake sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>⟦GLOBAL⟧</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Wind Aggs</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Splits</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>axes settled, measures open</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>2025</v>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Rate Development</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Rate change history — optional</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Fire + Nat Cat (money and events only)</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Triangles</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Loss development triangles</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Example Insurance SA</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>FX rates for conversion between currencies</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Loss share warning</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>0.2</v>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Collected step-2 blocks — written, never read</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
+          <t>Every dataset the tool knows, whether or not this pack carries it. The register above lists what is here; ⟦SECTIONS⟧ says which roles each section expects, so a missing sheet reads as structure rather than as a gap.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>⟦TYPES⟧</t>
+          <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Datasets</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>01, 02</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Windstorm</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Band from</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Band to</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Number of Risks</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Treaty type</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Fire + Nat Cat (money and events only)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Loss amount</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Number of Claims</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Date of Loss</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Event End Date</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>A field name carries one type across the whole workbook.</t>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Incurred Losses</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>yes | no</t>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Layered business</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>included | excluded</t>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>100% | ceded only</t>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Event Date | Event End Date</t>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>A field name carries one type across the whole workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>UW | Occurrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>yes | no</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>included | excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="7" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="10" t="n">
+    <row r="90">
+      <c r="B90" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="10" t="n">
+    <row r="91">
+      <c r="B91" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="10" t="n">
+    <row r="92">
+      <c r="B92" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="2" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="3" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="7" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="7" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="7" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C82" s="11" t="inlineStr">
+      <c r="C99" s="12" t="inlineStr">
         <is>
           <t>01.Premium@{N}</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F99" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="7" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E83" s="11" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F100" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C101" s="12" t="inlineStr">
         <is>
           <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F101" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="7" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C102" s="12" t="inlineStr">
         <is>
           <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E85" s="11" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F102" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>cat losses cannot exceed total incurred for the same year</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>03.Year basis</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>R-10</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>04.Year basis</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>history and cat losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Marker</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>Dataset_i = &lt;key&gt;</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Section_i = &lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>which section of the treaty block i belongs to</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Header_i</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>Header_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this column is block i's extraction column</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>Dataset_i = &lt;key&gt;</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>the same, declared as a hypothesis — raises a query</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2277,78 +2578,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2360,22 +2661,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2387,132 +2688,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>1240</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>15900</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>14930</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1310</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>16740</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>10030</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>1395</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>17520</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>12660</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1460</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>18390</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>11700</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1505</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>19200</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>10250</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>1180</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>14400</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>7100</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2522,15 +2823,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>8090</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>102150</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>66670</v>
       </c>
@@ -2573,78 +2874,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2656,22 +2957,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2683,132 +2984,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>860</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>6200</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>890</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>6450</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>915</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>6700</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>8900</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>940</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>6980</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>620</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>960</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>7250</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>540</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>745</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>5430</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>410</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2818,15 +3119,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>5310</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>39010</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>12150</v>
       </c>
@@ -2869,78 +3170,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2952,22 +3253,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2979,132 +3280,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>1020</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>7400</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>2300</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1055</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>7690</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>6800</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>1090</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>7980</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1450</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1125</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>8300</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>3200</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1150</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>8600</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>9100</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>890</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>6440</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>5300</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3114,15 +3415,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>6330</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>46410</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>28150</v>
       </c>
@@ -3163,59 +3464,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3227,17 +3528,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3249,75 +3550,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>18500</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>14400</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>19200</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>20900</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3327,7 +3628,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>73000</v>
       </c>
@@ -3338,7 +3639,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3375,59 +3676,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3439,17 +3740,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3461,75 +3762,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>7000</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>5430</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>7250</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>7900</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3539,7 +3840,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>27580</v>
       </c>
@@ -3550,7 +3851,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3587,59 +3888,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3651,17 +3952,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3673,75 +3974,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>8300</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>6440</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>8600</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>9250</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3751,7 +4052,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>32590</v>
       </c>
@@ -3762,7 +4063,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3802,93 +4103,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
@@ -3900,42 +4201,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Number of Claims</t>
         </is>
@@ -3952,7 +4253,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -3962,19 +4263,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>400</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3985,7 +4286,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3995,19 +4296,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>6800</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>188</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -4018,7 +4319,7 @@
           <t>EV-102</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4028,19 +4329,19 @@
           <t>Central Italy earthquake</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>950</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>44519</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>44520</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4051,11 +4352,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>SUM(E12:E14)</f>
         <v>8150</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <f>SUM(H12:H14)</f>
         <v>231</v>
       </c>
@@ -4066,14 +4367,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4113,88 +4414,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
@@ -4206,37 +4507,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
@@ -4253,7 +4554,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4263,16 +4564,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1400</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>44610</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>44611</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -4283,7 +4584,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -4293,16 +4594,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>44610</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="23" t="n">
         <v>44611</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -4313,7 +4614,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4323,16 +4624,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>45656</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>45659</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4343,7 +4644,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -4353,16 +4654,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>6600</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="23" t="n">
         <v>45656</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="23" t="n">
         <v>45659</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -4373,7 +4674,7 @@
           <t>EV-203</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4383,16 +4684,16 @@
           <t>Windstorm Kyrill II</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>45635</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="23" t="n">
         <v>45636</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -4403,7 +4704,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>SUM(E12:E16)</f>
         <v>14800</v>
       </c>
@@ -4414,14 +4715,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>

--- a/Intake_FireCatLosses_v1.xlsx
+++ b/Intake_FireCatLosses_v1.xlsx
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>axes settled, measures open</t>
+          <t>The cedent's book split — sums insured, one block per section</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>

--- a/Intake_FireCatLosses_v1.xlsx
+++ b/Intake_FireCatLosses_v1.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V120"/>
+  <dimension ref="B1:V122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2068,156 +2068,96 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="B93" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>at inception</t>
+        </is>
+      </c>
+    </row>
     <row r="94">
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>at expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="3" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
@@ -2226,7 +2166,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
@@ -2240,29 +2180,29 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
@@ -2275,38 +2215,38 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
@@ -2315,38 +2255,38 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -2360,186 +2300,266 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="7" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="7" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C104" s="12" t="inlineStr">
+      <c r="C106" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E104" s="12" t="inlineStr">
+      <c r="E106" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="F106" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="2" t="inlineStr">
+    <row r="108">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="3" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="7" t="inlineStr">
+    <row r="111">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="7" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireCatLosses_v1.xlsx
+++ b/Intake_FireCatLosses_v1.xlsx
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The rate change a submission claims — the UW's own sheet</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
